--- a/artfynd/A 882-2025 artfynd.xlsx
+++ b/artfynd/A 882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87311515</v>
+        <v>87311481</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817596.5693047582</v>
+        <v>817717</v>
       </c>
       <c r="R2" t="n">
-        <v>7314020.507989639</v>
+        <v>7313983</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,27 +746,18 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835193</v>
+        <v>91835201</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817413.995208819</v>
+        <v>817395</v>
       </c>
       <c r="R3" t="n">
-        <v>7314049.848243672</v>
+        <v>7314057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +844,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91835201</v>
+        <v>91835193</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817394.9976500734</v>
+        <v>817414</v>
       </c>
       <c r="R4" t="n">
-        <v>7314056.836975578</v>
+        <v>7314050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +941,9 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +967,111 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87311515</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvavaträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817597</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7314021</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 882-2025 artfynd.xlsx
+++ b/artfynd/A 882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,8 +1092,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87311515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>